--- a/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0001T0006Z000C1N75_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0001T0006Z000C1N75_analysis.xlsx
@@ -480,10 +480,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>3.650120809988104</v>
+        <v>0.5931446316230669</v>
       </c>
       <c r="D2" t="n">
-        <v>3.396070354861271</v>
+        <v>0.5518614326649565</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
